--- a/results/log_pv_cap_per_inst/log_pv_cap_per_inst_densities_pdensity_tests.xlsx
+++ b/results/log_pv_cap_per_inst/log_pv_cap_per_inst_densities_pdensity_tests.xlsx
@@ -451,27 +451,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>80.36***</t>
+          <t>82.37***</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.09***</t>
+          <t>15.18***</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6540.71***</t>
+          <t>7014.55***</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>44.29***</t>
+          <t>81.92***</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20.35***</t>
+          <t>55.96***</t>
         </is>
       </c>
     </row>
@@ -483,27 +483,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80.36***</t>
+          <t>82.37***</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.21***</t>
+          <t>5.08***</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6475.75***</t>
+          <t>6810.09***</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>11.79***</t>
+          <t>20.54***</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.35***</t>
+          <t>55.96***</t>
         </is>
       </c>
     </row>
@@ -515,27 +515,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>80.36***</t>
+          <t>82.37***</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.30***</t>
+          <t>4.11***</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6468.93***</t>
+          <t>6801.18***</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>8.69***</t>
+          <t>14.65***</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20.35***</t>
+          <t>55.96***</t>
         </is>
       </c>
     </row>
